--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>52.61</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>484092.0</t>
+          <t>395693.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>737857.46</t>
+          <t>745315.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-117225.28</v>
+        <v>-131296.38</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,32 +1455,32 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1490,27 +1490,27 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>682806.0</t>
+          <t>484092.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>732695.38</t>
+          <t>737857.46</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-75851.23</v>
+        <v>-117225.28</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,72 +1755,72 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-5.1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-11.68</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-3.06</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.61</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.77</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1418798.4</t>
+          <t>682806.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>725481.54</t>
+          <t>732695.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-26050.08</v>
+        <v>-75851.23</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>8734.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>46.24</t>
+          <t>46.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-67.25</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1698777.4</t>
+          <t>1418798.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1236211.4</t>
+          <t>1210220.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>719386.26</t>
+          <t>725481.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>132292.7594026387</t>
+          <t>107932.3220764736</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>40413.27</v>
+        <v>-26050.08</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16226.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-18.68</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.58000000000001</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>51.89</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-67.26</t>
+          <t>-67.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1863235.0</t>
+          <t>1698777.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1401013.9</t>
+          <t>1236211.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>715148.3</t>
+          <t>719386.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>462221</t>
+          <t>462566</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>148998.1204021616</t>
+          <t>132292.7594026387</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>149738.42</v>
+        <v>40413.27</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22364.0</t>
+          <t>16226.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-18.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.68</t>
+          <t>60.81</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>73.87</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.58000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>51.26</t>
+          <t>51.89</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-68.10</t>
+          <t>-67.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1298676.0</t>
+          <t>906568.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1867572.4</t>
+          <t>1863235.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1665281.1</t>
+          <t>1401013.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>698393.94</t>
+          <t>715148.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>202291</t>
+          <t>462221</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>148863.52099249</t>
+          <t>148998.1204021616</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>237931.32</v>
+        <v>149738.42</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>68694.0</t>
+          <t>22364.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-22.51</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>75.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.48</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>51.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.42</t>
+          <t>-68.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4097195.0</t>
+          <t>1298676.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1702695.6</t>
+          <t>1867572.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1699658.0</t>
+          <t>1665281.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>673412.06</t>
+          <t>698393.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>202291</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>132669.3755028237</t>
+          <t>148863.52099249</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>313412.07</v>
+        <v>237931.32</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32815.0</t>
+          <t>68694.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-24.84</t>
+          <t>-22.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.09</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>55.48</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>50.59</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-70.98</t>
+          <t>-69.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1869502.0</t>
+          <t>4097195.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1001642.0</t>
+          <t>1702695.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1392847.4</t>
+          <t>1699658.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>593224.76</t>
+          <t>673412.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-391205</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>99807.06823564472</t>
+          <t>132669.3755028237</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>110207.09</v>
+        <v>313412.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20984.0</t>
+          <t>32815.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-24.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-28.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>22.63</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>68.39</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>49.97</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.45</t>
+          <t>-70.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1144234.0</t>
+          <t>1869502.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>773645.4</t>
+          <t>1001642.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1261939.1</t>
+          <t>1392847.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>557149.36</t>
+          <t>593224.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-488293</t>
+          <t>-391205</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>97916.1550627848</t>
+          <t>99807.06823564472</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>54659.69</v>
+        <v>110207.09</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>27.97</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17276.0</t>
+          <t>20984.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.2</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.68</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.23</t>
+          <t>-72.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>928255.0</t>
+          <t>1144234.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>938792.8</t>
+          <t>773645.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1168784.3</t>
+          <t>1261939.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>535378.26</t>
+          <t>557149.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-229991</t>
+          <t>-488293</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>105780.9660021564</t>
+          <t>97916.1550627848</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>51061.43</v>
+        <v>54659.69</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9267.0</t>
+          <t>17276.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>-19.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>17.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>55.29</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>61.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>52.98</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.31</t>
+          <t>-73.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>690983.355907781</t>
+          <t>690991.8129496402</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>474292.0</t>
+          <t>928255.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1462989.8</t>
+          <t>938792.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1106862.5</t>
+          <t>1168784.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>519502.94</t>
+          <t>535378.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>356127</t>
+          <t>-229991</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>115729.973258437</t>
+          <t>105780.9660021564</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>67238.03</v>
+        <v>51061.43</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>17143.4</t>
+          <t>10771.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>5823.24</t>
+          <t>5760.5</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>1501.4</v>
+        <v>603.58</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5943,17 +5943,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>16774.8</t>
+          <t>17143.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>5739.88</t>
+          <t>5823.24</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>2367.58</v>
+        <v>1501.4</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.51</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>13648.0</t>
+          <t>16774.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>5386.6</t>
+          <t>5739.88</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1954.86</v>
+        <v>2367.58</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-14.51</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,98 +7022,98 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>93.58</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>111.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>13919.0</t>
+          <t>13648.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10532.3</t>
+          <t>11284.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>5296.48</t>
+          <t>5386.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1114.48842835234</t>
+          <t>1243.776040976043</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>2523.4</v>
+        <v>1954.86</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>93.58</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>262.82</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-96.15</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15494.6</t>
+          <t>13919.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9420.7</t>
+          <t>10532.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>5066.56</t>
+          <t>5296.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>858.3224254924266</t>
+          <t>1114.48842835234</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>2731.84</v>
+        <v>2523.4</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.41</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.25000000000001</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>410.91</t>
+          <t>262.82</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-98.68</t>
+          <t>-96.15</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4464.0</t>
+          <t>34781.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9451.6</t>
+          <t>15494.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6642.1</t>
+          <t>9420.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>4486.98</t>
+          <t>5066.56</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>517.6824746908645</t>
+          <t>858.3224254924266</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>732.51</v>
+        <v>2731.84</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.76</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,73 +8315,73 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>69.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.25000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>41.06</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -8391,22 +8391,22 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.56</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>13234.65</t>
+          <t>410.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-100.04</t>
+          <t>-98.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>5285.0</t>
+          <t>4464.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9291.8</t>
+          <t>9451.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6612.5</t>
+          <t>6642.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>4453.8</t>
+          <t>4486.98</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>478.6223621989851</t>
+          <t>517.6824746908645</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>1098.42</v>
+        <v>732.51</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.05</t>
+          <t>-18.76</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>85.33</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.07</t>
+          <t>41.06</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>402.35</t>
+          <t>13234.65</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-101.23</t>
+          <t>-100.04</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10813.0</t>
+          <t>5285.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>8920.6</t>
+          <t>9291.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6261.8</t>
+          <t>6612.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>4455.72</t>
+          <t>4453.8</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>365.9323302513665</t>
+          <t>478.6223621989851</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>1493.94</v>
+        <v>1098.42</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>511.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,52 +9198,52 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>85.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -9253,22 +9253,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>209.86</t>
+          <t>402.35</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-102.46</t>
+          <t>-101.23</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>22130.0</t>
+          <t>10813.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>7145.6</t>
+          <t>8920.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5618.0</t>
+          <t>6261.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>4298.2</t>
+          <t>4455.72</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>160.8391740361516</t>
+          <t>365.9323302513665</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>1413.34</v>
+        <v>1493.94</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>511.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>27.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.93000000000001</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40.79</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.07</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>68.88</t>
+          <t>209.86</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-103.75</t>
+          <t>-102.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4566.0</t>
+          <t>22130.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3346.8</t>
+          <t>7145.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3685.7</t>
+          <t>5618.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3901.26</t>
+          <t>4298.2</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-338</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-66.88872078657943</t>
+          <t>160.8391740361516</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>35.18</v>
+        <v>1413.34</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,47 +10060,47 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>22.58</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>40.93000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>68.88</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-103.75</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>79824.22910662825</t>
+          <t>79715.67841726619</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3665.0</t>
+          <t>4566.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3832.6</t>
+          <t>3346.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3367.4</t>
+          <t>3685.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3840.9</t>
+          <t>3901.26</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>-338</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-85.44749031398707</t>
+          <t>-66.88872078657943</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-53.01</v>
+        <v>35.18</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>214.16</t>
+          <t>224.57</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>52.19</t>
+          <t>51.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>258309.6</t>
+          <t>225541.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>752823.34</t>
+          <t>754339.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>163516</v>
+        <v>141265</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>52.51</t>
+          <t>52.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>309053.0</t>
+          <t>258309.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>750375.46</t>
+          <t>752823.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>127895</v>
+        <v>163516</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>52.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>377395.4</t>
+          <t>309053.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>748807.88</t>
+          <t>750375.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>230457</v>
+        <v>127895</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>395693.2</t>
+          <t>377395.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>745315.54</t>
+          <t>748807.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>464574</v>
+        <v>230457</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>52.61</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>484092.0</t>
+          <t>395693.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>737857.46</t>
+          <t>745315.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>305106</v>
+        <v>464574</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3244,27 +3244,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>682806.0</t>
+          <t>484092.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>732695.38</t>
+          <t>737857.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>417233</v>
+        <v>305106</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,72 +3514,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-8.67</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-3.36</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-13.48</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.61</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.77</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1418798.4</t>
+          <t>682806.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>725481.54</t>
+          <t>732695.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-26050.08321743459</t>
+          <t>-75851.23112288641</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>469607</v>
+        <v>417233</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>8734.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-15.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>46.24</t>
+          <t>46.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-67.25</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1698777.4</t>
+          <t>1418798.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1236211.4</t>
+          <t>1210220.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>719386.26</t>
+          <t>725481.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>132292.7594026387</t>
+          <t>107932.3220764736</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>40413.27390526235</t>
+          <t>-26050.08321743459</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>321946</v>
+        <v>469607</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16226.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-20.6</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,72 +4502,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>56.58000000000001</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.89</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-67.26</t>
+          <t>-67.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1863235.0</t>
+          <t>1698777.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1401013.9</t>
+          <t>1236211.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>715148.3</t>
+          <t>719386.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>462221</t>
+          <t>462566</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>148998.1204021616</t>
+          <t>132292.7594026387</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>149738.4171553557</t>
+          <t>40413.27390526235</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>906568</v>
+        <v>321946</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22364.0</t>
+          <t>16226.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-22.98</t>
+          <t>-22.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>75.68</t>
+          <t>60.81</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>73.87</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.58000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.26</t>
+          <t>51.89</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.10</t>
+          <t>-67.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1298676.0</t>
+          <t>906568.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1867572.4</t>
+          <t>1863235.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1665281.1</t>
+          <t>1401013.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>698393.94</t>
+          <t>715148.3</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>202291</t>
+          <t>462221</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>148863.52099249</t>
+          <t>148998.1204021616</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>237931.3211856545</t>
+          <t>149738.4171553557</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1298676</v>
+        <v>906568</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>68694.0</t>
+          <t>22364.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-24.49</t>
+          <t>-25.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>75.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.48</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>51.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.42</t>
+          <t>-68.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>689143.4269340974</t>
+          <t>688460.6716738198</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4097195.0</t>
+          <t>1298676.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1702695.6</t>
+          <t>1867572.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1699658.0</t>
+          <t>1665281.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>673412.06</t>
+          <t>698393.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>202291</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>132669.3755028237</t>
+          <t>148863.52099249</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>313412.0654723083</t>
+          <t>237931.3211856545</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>4097195</v>
+        <v>1298676</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,280 +5810,280 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>41.46</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-87.12</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>79285.89270386266</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>3043.2</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>10093.3</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>5362.4</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-7050</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>370.7494861735885</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-1010.262975570905</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>2767</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-4.650682237820038</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-31.92659851902614</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>6.977755118136152</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>10.98</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>17.08%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>6.65%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>235.15</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>無線寬頻網路應用設備95.59%、其他4.41% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>宇智-通信網路業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
         <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-86.19</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>79393.53653295129</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>10263.0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-6511</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>621.8426610362237</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-806.2180643579304</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>2040</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>宇智</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-4.650682237820038</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-31.92659851902614</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>6.977755118136152</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>5.94</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>17.08%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>6.65%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>225.11</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>無線寬頻網路應用設備95.59%、其他4.41% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>宇智-通信網路業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,94 +6130,94 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>7527.0</t>
+          <t>3751.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>5531.16</t>
+          <t>5439.54</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>2843</v>
+        <v>2040</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,74 +6566,74 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -6646,14 +6646,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8850.0</t>
+          <t>7527.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>5680.18</t>
+          <t>5531.16</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>4645</v>
+        <v>2843</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,22 +7012,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>10771.4</t>
+          <t>8850.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>5760.5</t>
+          <t>5680.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2921</v>
+        <v>4645</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>17143.4</t>
+          <t>10771.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>5823.24</t>
+          <t>5760.5</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>6307</v>
+        <v>2921</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>16774.8</t>
+          <t>17143.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>5739.88</t>
+          <t>5823.24</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>20919</v>
+        <v>6307</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>13648.0</t>
+          <t>16774.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>5386.6</t>
+          <t>5739.88</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1954.857910406408</t>
+          <t>2367.580989073429</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>9458</v>
+        <v>20919</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,98 +8841,98 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>93.58</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>111.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>13919.0</t>
+          <t>13648.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10532.3</t>
+          <t>11284.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>5296.48</t>
+          <t>5386.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1114.48842835234</t>
+          <t>1243.776040976043</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2523.401444081863</t>
+          <t>1954.857910406408</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>14252</v>
+        <v>9458</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9060,17 +9060,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>93.58</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>262.82</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-96.15</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>15494.6</t>
+          <t>13919.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9420.7</t>
+          <t>10532.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>5066.56</t>
+          <t>5296.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>858.3224254924266</t>
+          <t>1114.48842835234</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2731.842154901018</t>
+          <t>2523.401444081863</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>34781</v>
+        <v>14252</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>69.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.25000000000001</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>410.91</t>
+          <t>262.82</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.68</t>
+          <t>-96.15</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4464.0</t>
+          <t>34781.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9451.6</t>
+          <t>15494.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>6642.1</t>
+          <t>9420.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>4486.98</t>
+          <t>5066.56</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>517.6824746908645</t>
+          <t>858.3224254924266</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>732.5130933962018</t>
+          <t>2731.842154901018</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>4464</v>
+        <v>34781</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,73 +10149,73 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>69.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.25000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>41.06</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10225,22 +10225,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>42.56</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>13234.65</t>
+          <t>410.91</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-100.04</t>
+          <t>-98.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>79393.53653295129</t>
+          <t>79285.89270386266</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5285.0</t>
+          <t>4464.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>9291.8</t>
+          <t>9451.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6612.5</t>
+          <t>6642.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4453.8</t>
+          <t>4486.98</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>478.6223621989851</t>
+          <t>517.6824746908645</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1098.417537910887</t>
+          <t>732.5130933962018</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>5285</v>
+        <v>4464</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>225.11</t>
+          <t>235.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>45.73</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>47.69</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>141265.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>225541.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>225541.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>354816.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>754339.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>754339.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-185798.2351603996</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>141265</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>141265.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>46.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.19</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>163516.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>258309.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>258309.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>470557.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>752823.34</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>752823.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-183529.3073428617</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>163516</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>163516.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>46.67</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.51</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>127895.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>309053.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>309053</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>863925.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>750375.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>750375.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-176117.3994841338</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>127895</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>127895.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>48.11</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.22</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>230457.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>377395.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>377395.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1038086.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>748807.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>748807.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-155422.5168472321</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>230457</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>230457.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.68</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.12</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>464574.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>395693.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>395693.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1129464.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>745315.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>745315.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-131296.3803356857</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>464574</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>464574.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>51.76000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>305106.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>484092.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>484092</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1175832.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>737857.46</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>737857.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-117225.2788786306</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>305106</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>305106.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>53.74000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>46.77</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>417233.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>682806.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>682806</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1192750.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>732695.38</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>732695.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-75851.23112288641</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>417233</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>417233.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>55.38</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.54</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>469607.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1418798.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1418798.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1210220.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>725481.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>725481.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-26050.08321743459</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>469607</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>469607.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>56.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.24</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.24</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>321946.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1698777.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1698777.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1236211.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>719386.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>719386.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>40413.27390526235</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>321946</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>321946.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>51.89</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>906568.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1863235.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1863235</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1401013.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>715148.3</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>715148.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>149738.4171553557</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>906568</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>906568.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>56.44</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.65</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1298676.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1867572.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1867572.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1665281.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>698393.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>698393.9399999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>237931.3211856545</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1298676</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1298676.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>41.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2767.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3043.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3043.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>10093.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5362.4</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5362.4</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1010.262975570905</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2767</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2767.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.42</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2040.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3751.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3751.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10263.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5439.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5439.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-806.2180643579304</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2040</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>43.22</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2843.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>7527.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>7527</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>10587.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5531.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5531.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-408.0389746123274</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2843</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2843.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>43.68</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>42.32</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.38</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>4645.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>8850.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>8850</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>11384.5</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5680.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5680.18</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>89.32540268897355</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>4645</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>4645.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>42.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2921.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>10771.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>10771.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>13133.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5760.5</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5760.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>603.5843201662283</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2921</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2921.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>44.69</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.33</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6307.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>17143.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>17143.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>13297.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5823.24</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5823.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1501.397619413508</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6307</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6307.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.94</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.3</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>20919.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>16774.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>16774.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>13033.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5739.88</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5739.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2367.580989073429</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>20919</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>20919.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.24</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>9458.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>13648.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>13648</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>11284.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5386.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1954.857910406408</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>9458</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>9458.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>14252.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>13919.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>13919</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>10532.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5296.48</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5296.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2523.401444081863</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>14252</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>14252.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>43.07</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.12</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>34781.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>15494.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>15494.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9420.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5066.56</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5066.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2731.842154901018</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>34781</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>34781.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>42.25000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>4464.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9451.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9451.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>6642.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4486.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4486.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>732.5130933962018</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>4464</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>4464.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>52.61</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.77</v>
+        <v>46.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>682806</v>
+        <v>484092</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>732695.38</v>
+        <v>737857.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,72 +3908,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-5.77</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-15.48</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-3.36</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.53</v>
+        <v>52.61</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.54</v>
+        <v>46.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1418798.4</v>
+        <v>682806</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>725481.54</v>
+        <v>732695.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-26050.08321743459</t>
+          <t>-75851.23112288641</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>8734.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.25</v>
+        <v>52.53</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.24</v>
+        <v>46.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-67.25</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1698777.4</v>
+        <v>1418798.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1236211.4</t>
+          <t>1210220.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>719386.26</v>
+        <v>725481.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>132292.7594026387</t>
+          <t>107932.3220764736</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>40413.27390526235</t>
+          <t>-26050.08321743459</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16226.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-22.72</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.58000000000001</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>51.89</v>
+        <v>52.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.96</v>
+        <v>46.24</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-67.26</t>
+          <t>-67.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1863235</v>
+        <v>1698777.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1401013.9</t>
+          <t>1236211.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>715148.3</v>
+        <v>719386.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>462221</t>
+          <t>462566</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>148998.1204021616</t>
+          <t>132292.7594026387</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>149738.4171553557</t>
+          <t>40413.27390526235</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22364.0</t>
+          <t>16226.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-25.14</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>75.68</t>
+          <t>60.81</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>73.87</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.58000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>51.26</v>
+        <v>51.89</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.65</v>
+        <v>45.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.10</t>
+          <t>-67.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>688460.6716738198</t>
+          <t>687694.7250000001</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1298676.0</t>
+          <t>906568.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1867572.4</v>
+        <v>1863235</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1665281.1</t>
+          <t>1401013.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>698393.9399999999</v>
+        <v>715148.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>202291</t>
+          <t>462221</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>148863.52099249</t>
+          <t>148998.1204021616</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>237931.3211856545</t>
+          <t>149738.4171553557</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1298676.0</t>
+          <t>906568.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,70 +6179,70 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,72 +6488,72 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,74 +6918,74 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -6998,14 +6998,14 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,22 +7358,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.3</v>
+        <v>41.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>16774.8</v>
+        <v>17143.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5739.88</v>
+        <v>5823.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>41.77</v>
+        <v>41.94</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.24</v>
+        <v>41.3</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13648</v>
+        <v>16774.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5386.6</v>
+        <v>5739.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1954.857910406408</t>
+          <t>2367.580989073429</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,22 +9163,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>93.58</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.6</v>
+        <v>41.77</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.18</v>
+        <v>41.24</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>111.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13919</v>
+        <v>13648</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10532.3</t>
+          <t>11284.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5296.48</v>
+        <v>5386.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1114.48842835234</t>
+          <t>1243.776040976043</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2523.401444081863</t>
+          <t>1954.857910406408</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>93.58</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.36</v>
+        <v>41.6</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.12</v>
+        <v>41.18</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>262.82</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-96.15</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>15494.6</v>
+        <v>13919</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>9420.7</t>
+          <t>10532.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5066.56</v>
+        <v>5296.48</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>858.3224254924266</t>
+          <t>1114.48842835234</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2731.842154901018</t>
+          <t>2523.401444081863</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.33</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>42.25000000000001</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.06</v>
+        <v>41.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.06</v>
+        <v>41.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>410.91</t>
+          <t>262.82</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.68</t>
+          <t>-96.15</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>79285.89270386266</t>
+          <t>79181.11285714286</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4464.0</t>
+          <t>34781.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>9451.6</v>
+        <v>15494.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6642.1</t>
+          <t>9420.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>4486.98</v>
+        <v>5066.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>517.6824746908645</t>
+          <t>858.3224254924266</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>732.5130933962018</t>
+          <t>2731.842154901018</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>4464.0</t>
+          <t>34781.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>235.15</t>
+          <t>234.51</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
         <v>52.61</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.77</v>
+        <v>46.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>682806</v>
+        <v>484092</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>732695.38</v>
+        <v>737857.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,72 +4338,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-5.77</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-12.39</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.53</v>
+        <v>52.61</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.54</v>
+        <v>46.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1418798.4</v>
+        <v>682806</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>725481.54</v>
+        <v>732695.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-26050.08321743459</t>
+          <t>-75851.23112288641</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>8734.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.25</v>
+        <v>52.53</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.24</v>
+        <v>46.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-67.25</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1698777.4</v>
+        <v>1418798.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1236211.4</t>
+          <t>1210220.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>719386.26</v>
+        <v>725481.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>132292.7594026387</t>
+          <t>107932.3220764736</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>40413.27390526235</t>
+          <t>-26050.08321743459</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16226.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>73.87</t>
+          <t>53.07</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.58000000000001</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>51.89</v>
+        <v>52.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.96</v>
+        <v>46.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-67.26</t>
+          <t>-67.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>687694.7250000001</t>
+          <t>687062.6019971468</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1863235</v>
+        <v>1698777.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1401013.9</t>
+          <t>1236211.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>715148.3</v>
+        <v>719386.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>462221</t>
+          <t>462566</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>148998.1204021616</t>
+          <t>132292.7594026387</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>149738.4171553557</t>
+          <t>40413.27390526235</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>906568.0</t>
+          <t>321946.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,75 +6604,75 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,72 +6918,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,74 +7348,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -7428,14 +7428,14 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,22 +7788,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.3</v>
+        <v>41.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>16774.8</v>
+        <v>17143.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5739.88</v>
+        <v>5823.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.77</v>
+        <v>41.94</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.24</v>
+        <v>41.3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13648</v>
+        <v>16774.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5386.6</v>
+        <v>5739.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1954.857910406408</t>
+          <t>2367.580989073429</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,94 +9593,94 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>93.58</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.6</v>
+        <v>41.77</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.18</v>
+        <v>41.24</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>111.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13919</v>
+        <v>13648</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10532.3</t>
+          <t>11284.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5296.48</v>
+        <v>5386.6</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1114.48842835234</t>
+          <t>1243.776040976043</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2523.401444081863</t>
+          <t>1954.857910406408</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>93.58</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.36</v>
+        <v>41.6</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.12</v>
+        <v>41.18</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>262.82</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-96.15</t>
+          <t>-93.21</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>79181.11285714286</t>
+          <t>79080.02353780314</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>15494.6</v>
+        <v>13919</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9420.7</t>
+          <t>10532.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5066.56</v>
+        <v>5296.48</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>858.3224254924266</t>
+          <t>1114.48842835234</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2731.842154901018</t>
+          <t>2523.401444081863</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>34781.0</t>
+          <t>14252.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>234.51</t>
+          <t>236.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1964.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3447.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,176 +1014,176 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-8.68</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>46.28</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-554.16</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-101.78</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>686276.8824786325</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>131937.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>220495.4</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>753091.54</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-88557</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-115339.9696769817</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-170937.5362407448</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-9.37</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>45.21</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-1616.24</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-99.31</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>687062.6019971468</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>139451.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>258423.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>757640.24</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-118971</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-105231.321210843</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-176410.8291751111</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>18.22810759778194</t>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN9" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>52.61</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.77</v>
+        <v>46.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>682806</v>
+        <v>484092</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>732695.38</v>
+        <v>737857.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,72 +4768,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-7.84</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.86</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-12.39</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.53</v>
+        <v>52.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.54</v>
+        <v>46.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1418798.4</v>
+        <v>682806</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>725481.54</v>
+        <v>732695.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-26050.08321743459</t>
+          <t>-75851.23112288641</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>8734.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-14.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.07</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.25</v>
+        <v>52.53</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.24</v>
+        <v>46.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-67.25</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>687062.6019971468</t>
+          <t>686276.8824786325</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1698777.4</v>
+        <v>1418798.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1236211.4</t>
+          <t>1210220.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>719386.26</v>
+        <v>725481.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>462566</t>
+          <t>208578</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>132292.7594026387</t>
+          <t>107932.3220764736</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>40413.27390526235</t>
+          <t>-26050.08321743459</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>321946.0</t>
+          <t>469607.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,84 +5723,84 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,75 +7034,75 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,72 +7348,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,74 +7778,74 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>4.41</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-2.02</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -7858,14 +7858,14 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,22 +8218,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.3</v>
+        <v>41.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>16774.8</v>
+        <v>17143.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5739.88</v>
+        <v>5823.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.77</v>
+        <v>41.94</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.24</v>
+        <v>41.3</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13648</v>
+        <v>16774.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5386.6</v>
+        <v>5739.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1954.857910406408</t>
+          <t>2367.580989073429</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,94 +10023,94 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>93.58</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.6</v>
+        <v>41.77</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.18</v>
+        <v>41.24</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.47</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>111.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.21</t>
+          <t>-90.60</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>79080.02353780314</t>
+          <t>78973.3952991453</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>13919</v>
+        <v>13648</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10532.3</t>
+          <t>11284.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5296.48</v>
+        <v>5386.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1114.48842835234</t>
+          <t>1243.776040976043</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2523.401444081863</t>
+          <t>1954.857910406408</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14252.0</t>
+          <t>9458.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>236.93</t>
+          <t>235.92</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,42 +1313,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1964.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3447.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,166 +1454,166 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-8.68</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>46.28</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-554.16</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-101.78</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>685468.5725462305</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>131937.8</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>220495.4</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>753091.54</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-88557</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-115339.9696769817</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-170937.5362407448</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-9.37</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>45.21</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-1616.24</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-99.31</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>686276.8824786325</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>139451.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>258423.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>757640.24</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-118971</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-105231.321210843</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-176410.8291751111</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>18.22810759778194</t>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>52.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.77</v>
+        <v>46.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>682806</v>
+        <v>484092</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>732695.38</v>
+        <v>737857.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8734.0</t>
+          <t>8272.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-7.84</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-42.75</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-14.6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.86</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>17.23</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-7.89</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>53.74000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.53</v>
+        <v>52.61</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.54</v>
+        <v>46.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-69.92</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>686276.8824786325</t>
+          <t>685468.5725462305</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1418798.4</v>
+        <v>682806</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1210220.2</t>
+          <t>1192750.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>725481.54</v>
+        <v>732695.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>208578</t>
+          <t>-509944</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>107932.3220764736</t>
+          <t>79657.92927657203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-26050.08321743459</t>
+          <t>-75851.23112288641</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>469607.0</t>
+          <t>417233.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,84 +6153,84 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,75 +7464,75 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,72 +7778,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,74 +8208,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,22 +8648,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.3</v>
+        <v>41.33</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>16774.8</v>
+        <v>17143.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5739.88</v>
+        <v>5823.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>67.07</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>75.75</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.77</v>
+        <v>41.94</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.24</v>
+        <v>41.3</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-90.60</t>
+          <t>-88.24</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78973.3952991453</t>
+          <t>78865.10739687055</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>13648</v>
+        <v>16774.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11284.3</t>
+          <t>13033.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5386.6</v>
+        <v>5739.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1243.776040976043</t>
+          <t>1416.669109914102</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1954.857910406408</t>
+          <t>2367.580989073429</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>9458.0</t>
+          <t>20919.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>235.92</t>
+          <t>237.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,176 +1874,176 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-8.68</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>46.28</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-554.16</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-101.78</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>684794.0092329546</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>131937.8</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>220495.4</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>753091.54</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-88557</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-115339.9696769817</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-170937.5362407448</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-9.37</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>45.21</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-1616.24</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-99.31</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>685468.5725462305</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>139451.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>258423.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>757640.24</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-118971</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-105231.321210843</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-176410.8291751111</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BN4" t="inlineStr">
         <is>
           <t>18.22810759778194</t>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8272.0</t>
+          <t>6357.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-58.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-7.89</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.74000000000001</t>
+          <t>51.76000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>52.61</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.77</v>
+        <v>46.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-44.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.92</t>
+          <t>-72.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>685468.5725462305</t>
+          <t>684794.0092329546</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>682806</v>
+        <v>484092</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1192750.8</t>
+          <t>1175832.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>732695.38</v>
+        <v>737857.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-509944</t>
+          <t>-691740</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>79657.92927657203</t>
+          <t>49368.20494500239</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-75851.23112288641</t>
+          <t>-117225.2788786306</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>417233.0</t>
+          <t>305106.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.88</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,22 +5723,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>56.03</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,22 +6583,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -6609,58 +6609,58 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,70 +7899,70 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,72 +8208,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,74 +8638,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -8718,14 +8718,14 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>67.07</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>59.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.94</v>
+        <v>42.08</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.3</v>
+        <v>41.33</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-88.24</t>
+          <t>-86.54</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78865.10739687055</t>
+          <t>78757.57670454546</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>16774.8</v>
+        <v>17143.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13033.3</t>
+          <t>13297.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5739.88</v>
+        <v>5823.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1416.669109914102</t>
+          <t>1429.704265221703</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2367.580989073429</t>
+          <t>1501.397619413508</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>20919.0</t>
+          <t>6307.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>237.74</t>
+          <t>256.91</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>45.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>78.61</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-114.05</t>
+          <t>-74.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,176 +2304,176 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-8.68</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>46.28</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-554.16</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-101.78</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>683992.8212765958</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>131937.8</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>220495.4</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>753091.54</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-88557</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-115339.9696769817</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-170937.5362407448</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-9.37</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>45.21</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-1616.24</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-99.31</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>684794.0092329546</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>139451.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>258423.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>757640.24</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-118971</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-105231.321210843</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-176410.8291751111</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
           <t>18.22810759778194</t>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-9.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-61.02</t>
+          <t>-90.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6357.0</t>
+          <t>9905.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-58.83</t>
+          <t>-64.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.76000000000001</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.61</v>
+        <v>52.68</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.96</v>
+        <v>47.12</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-44.15</t>
+          <t>-61.02</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-76.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>684794.0092329546</t>
+          <t>683992.8212765958</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>484092</v>
+        <v>395693.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1175832.2</t>
+          <t>1129464.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>737857.46</v>
+        <v>745315.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-691740</t>
+          <t>-733770</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>49368.20494500239</t>
+          <t>21573.65336335807</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-117225.2788786306</t>
+          <t>-131296.3803356857</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>305106.0</t>
+          <t>464574.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>31.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>43.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,54 +5744,54 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>56.03</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.73</v>
+        <v>41.79</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.85</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.30</t>
+          <t>-89.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3266</v>
+        <v>3641.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3154.6</t>
+          <t>3446.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5369.36</v>
+        <v>5420.44</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>195</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-439.4624580812879</t>
+          <t>-504.8901871323186</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1149.975956771535</t>
+          <t>-864.7426969129874</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,33 +6153,33 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>56.03</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,84 +7013,84 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,75 +8324,75 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,72 +8638,72 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,74 +9068,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.77</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -9148,14 +9148,14 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,22 +9508,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>59.67</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.08</v>
+        <v>42.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>34.72</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-86.54</t>
+          <t>-85.26</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78757.57670454546</t>
+          <t>78658.28297872341</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>17143.4</v>
+        <v>10771.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13297.5</t>
+          <t>13133.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5823.24</v>
+        <v>5760.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>-2361</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1429.704265221703</t>
+          <t>1302.608889059322</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1501.397619413508</t>
+          <t>603.5843201662283</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>6307.0</t>
+          <t>2921.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>256.91</t>
+          <t>251.61</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>13274.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.61</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-6.34</t>
-        </is>
+          <t>87.96</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-4.35</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.7</v>
+        <v>49.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.32</v>
+        <v>48.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-74.29</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>110484.2</v>
+        <v>211915.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>131708.6</t>
+          <t>175683.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>704283.76</v>
+        <v>699484.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-21224</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-129126.1153547128</t>
+          <t>-122654.2741962539</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-141058.6253221495</t>
+          <t>-87059.14782473008</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1288,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.61</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-7.05</t>
-        </is>
+          <t>78.61</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-6.34</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-114.05</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.47</t>
-        </is>
+          <t>-74.29</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.57</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1710,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>59.47</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-8.16</t>
-        </is>
+          <t>76.61</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-7.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-214.93</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
+          <t>-114.05</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.47</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2132,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>45.67</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-8.68</t>
-        </is>
+          <t>59.47</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-8.16</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-554.16</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>-214.93</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.33</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2554,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,176 +2702,168 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.96</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+          <t>45.67</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>46.28</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>45.25</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-554.16</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-101.78</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>684447.947592068</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>131937.8</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>220495.4</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>753091.54</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-88557</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-115339.9696769817</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-170937.5362407448</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>90325.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-9.37</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>6.29</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>45.21</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-1616.24</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-99.31</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>683992.8212765958</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>139451.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>258423.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>757640.24</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-118971</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-105231.321210843</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-176410.8291751111</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>163051.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>18.22810759778194</t>
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +2976,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.77</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-10.99</t>
-        </is>
+          <t>30.96</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-9.369999999999999</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-381.16</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+          <t>-1616.24</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.06</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3446,7 +3398,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-11.34</t>
-        </is>
+          <t>20.77</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-10.99</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-229.04</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+          <t>-381.16</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.3</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3820,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.02</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-11.79</t>
-        </is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-11.34</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-154.91</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
+          <t>-229.04</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.58</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4242,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-2.72</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-11.13</t>
-        </is>
+      <c r="AH10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-11.79</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-120.41</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
+          <t>-154.91</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.92</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-8.02</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-8.61</t>
-        </is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-11.13</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-90.82</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+          <t>-120.41</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.28</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5086,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9905.0</t>
+          <t>5126.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.97</t>
+          <t>-63.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5332,56 +5252,48 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-5.10</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-8.609999999999999</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.11</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.68</v>
+        <v>52.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>44.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-61.02</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
+          <t>-90.82</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.66</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.50</t>
+          <t>-80.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>683992.8212765958</t>
+          <t>684447.947592068</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>395693.2</v>
+        <v>377395.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1129464.1</t>
+          <t>1038086.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>745315.54</v>
+        <v>748807.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-733770</t>
+          <t>-660691</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>21573.65336335807</t>
+          <t>-5656.526669040424</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-131296.3803356857</t>
+          <t>-155422.5168472321</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>464574.0</t>
+          <t>230457.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,74 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>63.83</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+          <t>72.39</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.27</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.32</v>
+        <v>43.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.79</v>
+        <v>41.84</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-5.53</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+          <t>-3.01</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.46</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5820,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3641.4</v>
+        <v>2879.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3446.2</t>
+          <t>3155.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5420.44</v>
+        <v>5432</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-504.8901871323186</t>
+          <t>-573.5164425872202</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-864.7426969129874</t>
+          <t>-950.9608475891796</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5835,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,54 +6078,50 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>56.03</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
+          <t>63.83</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.59</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.73</v>
+        <v>41.79</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,18 +6130,14 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.85</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+          <t>-5.53</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.46</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6250,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.30</t>
+          <t>-89.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3266</v>
+        <v>3641.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3154.6</t>
+          <t>3446.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5369.36</v>
+        <v>5420.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>195</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-439.4624580812879</t>
+          <t>-504.8901871323186</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1149.975956771535</t>
+          <t>-864.7426969129874</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6257,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,33 +6479,33 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,59 +6515,51 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>69.14</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+          <t>56.03</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.32</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.35</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.08</v>
+        <v>43.21</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.69</v>
+        <v>41.73</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.47</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6680,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6694,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6744,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,7 +6754,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,74 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>64.29</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
+          <t>69.14</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.4</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.47</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+          <t>-12.59</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.49</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -7110,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7111,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,95 +7323,87 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>49.07</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
+          <t>64.29</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.24</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-10.12</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>-8.47</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.5</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7540,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7533,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,74 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20.63</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
+          <t>49.07</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-28.73</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+          <t>-10.12</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.52</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7970,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +7955,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,74 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
+          <t>20.63</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.73</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-28.81</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+          <t>-28.73</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.53</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8400,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8367,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8432,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8447,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,74 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.29</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-1.50</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.42</v>
+        <v>41.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.57</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8830,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,72 +8916,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>4.77</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +8996,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,74 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.57</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.67</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
+          <t>-24.76</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.61</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9260,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9110,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9211,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9313,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,74 +9338,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -9578,14 +9418,14 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -9593,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,74 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.43</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-3.16</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
+          <t>19.26</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.94</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>9.32</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+          <t>-11.67</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.64</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9690,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9735,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,22 +9770,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9993,7 +9825,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,12 +9840,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,74 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>53.19</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+          <t>33.43</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3.22</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.22</v>
+        <v>42.32</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>34.72</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>9.32</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.66</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -10120,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-85.26</t>
+          <t>-84.91</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +9954,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78658.28297872341</t>
+          <t>78550.559490085</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>10771.4</v>
+        <v>8850</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13133.0</t>
+          <t>11384.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5760.5</v>
+        <v>5680.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2361</t>
+          <t>-2534</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1302.608889059322</t>
+          <t>1115.949891156192</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>603.5843201662283</t>
+          <t>89.32540268897355</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2921.0</t>
+          <t>4645.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>251.61</t>
+          <t>251.1</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13274.0</t>
+          <t>43439.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,14 +1033,14 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>7.95</v>
+        <v>10.89</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4.35</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1050,30 +1050,30 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.58</v>
+        <v>49.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.4</v>
+        <v>48.58</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.58</v>
+        <v>-0.47</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,53 +1082,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>211915.6</v>
+        <v>660301.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>175683.7</t>
+          <t>396119.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>699484.86</v>
+        <v>707273.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>264181</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-122654.2741962539</t>
+          <t>-91850.48737850999</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-87059.14782473008</t>
+          <t>77570.34011908178</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>13274.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.61</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.7</v>
+        <v>49.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.32</v>
+        <v>48.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-74.29</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1</v>
+        <v>-0.62</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>110484.2</v>
+        <v>211915.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>131708.6</t>
+          <t>175683.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>704283.76</v>
+        <v>699484.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-21224</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-129126.1153547128</t>
+          <t>-122654.2741962539</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-141058.6253221495</t>
+          <t>-87059.14782473008</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>78.61</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-7.05</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-114.05</t>
+          <t>-74.29</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>-1</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-10.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.06</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>-8.16</v>
+        <v>-7.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.82</v>
+        <v>0.06</v>
       </c>
       <c r="AI6" t="n">
-        <v>-8.68</v>
+        <v>-8.16</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,53 +2770,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="AI7" t="n">
-        <v>-9.369999999999999</v>
+        <v>-8.68</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>46.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.95</v>
+        <v>50.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.06</v>
+        <v>48.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1616.24</t>
+          <t>-554.16</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.9</v>
+        <v>-1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.31</t>
+          <t>-101.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>139451.8</v>
+        <v>131937.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>258423.6</t>
+          <t>220495.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>757640.24</v>
+        <v>753091.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-118971</t>
+          <t>-88557</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-105231.321210843</t>
+          <t>-115339.9696769817</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-176410.8291751111</t>
+          <t>-170937.5362407448</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" t="n">
-        <v>-10.99</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.84</v>
+        <v>-0.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.39</v>
+        <v>2.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>-11.34</v>
+        <v>-10.99</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.75</v>
+        <v>-0.84</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.67</v>
+        <v>-0.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>-11.79</v>
+        <v>-11.34</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,53 +4458,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH11" t="n">
-        <v>-2.72</v>
+        <v>0.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>-11.13</v>
+        <v>-11.79</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,53 +4880,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5126.0</t>
+          <t>2841.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-63.65</t>
+          <t>-64.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>143</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-8.02</v>
+        <v>-2.72</v>
       </c>
       <c r="AI12" t="n">
-        <v>-8.609999999999999</v>
+        <v>-11.13</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.64</v>
+        <v>52.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.22</v>
+        <v>47.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.85</t>
+          <t>-85.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>684447.947592068</t>
+          <t>688428.0487977369</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>377395.4</v>
+        <v>309053</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1038086.4</t>
+          <t>863925.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>748807.88</v>
+        <v>750375.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-660691</t>
+          <t>-554872</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5656.526669040424</t>
+          <t>-31881.27633290095</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-155422.5168472321</t>
+          <t>-176117.3994841338</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>230457.0</t>
+          <t>127895.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>59.89</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,67 +5656,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.36</v>
+        <v>43.42</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.84</v>
+        <v>41.89</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AQ13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR13" t="n">
         <v>0.45</v>
       </c>
-      <c r="AR13" t="n">
-        <v>0.46</v>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2879.8</v>
+        <v>3015</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3155.4</t>
+          <t>3220.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5432</v>
+        <v>5433.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-205</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-573.5164425872202</t>
+          <t>-616.9392255542301</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-950.9608475891796</t>
+          <t>-855.7645318727846</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,63 +6078,63 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.96</v>
+        <v>0.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.32</v>
+        <v>43.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.79</v>
+        <v>41.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AR14" t="n">
         <v>0.46</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3641.4</v>
+        <v>2879.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3446.2</t>
+          <t>3155.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5420.44</v>
+        <v>5432</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-504.8901871323186</t>
+          <t>-573.5164425872202</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-864.7426969129874</t>
+          <t>-950.9608475891796</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6257,22 +6257,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,50 +6500,50 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>56.03</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-0.58</v>
+        <v>0.96</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.73</v>
+        <v>41.79</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6552,14 +6552,14 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.85</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.30</t>
+          <t>-89.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3266</v>
+        <v>3641.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3154.6</t>
+          <t>3446.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5369.36</v>
+        <v>5420.44</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>195</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-439.4624580812879</t>
+          <t>-504.8901871323186</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1149.975956771535</t>
+          <t>-864.7426969129874</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6679,22 +6679,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6901,33 +6901,33 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -6937,51 +6937,51 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>56.03</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-0.35</v>
+        <v>-0.58</v>
       </c>
       <c r="AI16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.43</v>
-      </c>
       <c r="AR16" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>0.93</v>
+        <v>-0.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,87 +7745,87 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>3.53</v>
+        <v>0.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.17</v>
+        <v>0.24</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ18" t="n">
         <v>0.46</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,66 +8188,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>1.18</v>
+        <v>3.53</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,67 +9032,67 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>-1.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI21" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR21" t="n">
         <v>0.57</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9211,22 +9211,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,72 +9338,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-3.05</v>
+        <v>-1.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.94</v>
+        <v>0.57</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,48 +9532,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9735,7 +9735,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,74 +9760,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-28.91</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-22.26</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>42.3</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>52.9</t>
@@ -9840,14 +9840,14 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>-18.18</t>
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-3.16</v>
+        <v>-3.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.22</v>
+        <v>1.94</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.32</v>
+        <v>42.4</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.38</v>
+        <v>41.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-84.91</t>
+          <t>-85.34</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78550.559490085</t>
+          <t>78446.8684582744</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>8850</v>
+        <v>7527</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11384.5</t>
+          <t>10587.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5680.18</v>
+        <v>5531.16</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2534</t>
+          <t>-3060</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1115.949891156192</t>
+          <t>881.4900656533426</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>89.32540268897355</t>
+          <t>-408.0389746123274</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>4645.0</t>
+          <t>2843.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>251.1</t>
+          <t>250.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43439.0</t>
+          <t>10408.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,147 +933,147 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>10.89</v>
+        <v>6.06</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.45</v>
+        <v>2.97</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.37</v>
+        <v>49.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.58</v>
+        <v>48.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>208.23</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.05</v>
+        <v>0.34</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-103.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>660301.2</v>
+        <v>756681.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>396119.5</t>
+          <t>435826.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>707273.86</v>
+        <v>711662.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>264181</t>
+          <t>320854</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-91850.48737850999</t>
+          <t>-68797.0280623126</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>77570.34011908178</t>
+          <t>57996.99817677308</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13274.0</t>
+          <t>43439.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1355,49 +1355,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,27 +1405,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,14 +1455,14 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>7.95</v>
+        <v>10.89</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4.35</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1472,30 +1472,30 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.58</v>
+        <v>49.37</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.4</v>
+        <v>48.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.58</v>
+        <v>-0.47</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>211915.6</v>
+        <v>660301.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>175683.7</t>
+          <t>396119.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>699484.86</v>
+        <v>707273.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>264181</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-122654.2741962539</t>
+          <t>-91850.48737850999</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-87059.14782473008</t>
+          <t>77570.34011908178</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>13274.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1777,49 +1777,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.61</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.7</v>
+        <v>49.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.32</v>
+        <v>48.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-74.29</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1</v>
+        <v>-0.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>110484.2</v>
+        <v>211915.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>131708.6</t>
+          <t>175683.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>704283.76</v>
+        <v>699484.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-21224</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-129126.1153547128</t>
+          <t>-122654.2741962539</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-141058.6253221495</t>
+          <t>-87059.14782473008</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2199,49 +2199,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>78.61</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-7.05</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-114.05</t>
+          <t>-74.29</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>-1</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2621,49 +2621,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2671,27 +2671,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.06</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>-8.16</v>
+        <v>-7.05</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3043,49 +3043,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.82</v>
+        <v>0.06</v>
       </c>
       <c r="AI7" t="n">
-        <v>-8.68</v>
+        <v>-8.16</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3465,49 +3465,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3515,27 +3515,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>-9.369999999999999</v>
+        <v>-8.68</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>46.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.95</v>
+        <v>50.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.06</v>
+        <v>48.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1616.24</t>
+          <t>-554.16</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.9</v>
+        <v>-1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.31</t>
+          <t>-101.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>139451.8</v>
+        <v>131937.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>258423.6</t>
+          <t>220495.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>757640.24</v>
+        <v>753091.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-118971</t>
+          <t>-88557</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-105231.321210843</t>
+          <t>-115339.9696769817</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-176410.8291751111</t>
+          <t>-170937.5362407448</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3887,49 +3887,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3937,27 +3937,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="AI9" t="n">
-        <v>-10.99</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.84</v>
+        <v>-0.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4309,49 +4309,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4359,27 +4359,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.39</v>
+        <v>2.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>-11.34</v>
+        <v>-10.99</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.75</v>
+        <v>-0.84</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4731,49 +4731,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4781,27 +4781,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.67</v>
+        <v>-0.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>-11.79</v>
+        <v>-11.34</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2841.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.23</t>
+          <t>-45.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5153,49 +5153,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-27 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>47.95</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>45.15</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5203,27 +5203,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>9.02</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
       <c r="AH12" t="n">
-        <v>-2.72</v>
+        <v>0.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>-11.13</v>
+        <v>-11.79</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.04</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.51</v>
+        <v>52.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.36</v>
+        <v>47.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-154.91</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-89.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>688428.0487977369</t>
+          <t>688643.3834745763</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>309053</v>
+        <v>258309.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>863925.7</t>
+          <t>470557.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>750375.46</v>
+        <v>752823.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-554872</t>
+          <t>-212248</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-31881.27633290095</t>
+          <t>-55211.74264212567</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-176117.3994841338</t>
+          <t>-183529.3073428617</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>127895.0</t>
+          <t>163516.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>59.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.71</v>
+        <v>0.02</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>43.49</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.42</v>
+        <v>43.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.89</v>
+        <v>41.94</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>-90.10</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3494.0</t>
+          <t>2748.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3015</v>
+        <v>3185</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3220.5</t>
+          <t>3291.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5433.74</v>
+        <v>5467.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-205</t>
+          <t>-106</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-616.9392255542301</t>
+          <t>-648.7459597111929</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-855.7645318727846</t>
+          <t>-823.6829975744886</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>3494.0</t>
+          <t>2748.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,67 +6078,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.36</v>
+        <v>43.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.84</v>
+        <v>41.89</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AQ14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR14" t="n">
         <v>0.45</v>
       </c>
-      <c r="AR14" t="n">
-        <v>0.46</v>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2879.8</v>
+        <v>3015</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3155.4</t>
+          <t>3220.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5432</v>
+        <v>5433.74</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-205</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-573.5164425872202</t>
+          <t>-616.9392255542301</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-950.9608475891796</t>
+          <t>-855.7645318727846</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,63 +6500,63 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>0.96</v>
+        <v>0.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.32</v>
+        <v>43.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.79</v>
+        <v>41.84</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AR15" t="n">
         <v>0.46</v>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3641.4</v>
+        <v>2879.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3446.2</t>
+          <t>3155.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5420.44</v>
+        <v>5432</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-504.8901871323186</t>
+          <t>-573.5164425872202</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-864.7426969129874</t>
+          <t>-950.9608475891796</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,22 +6679,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,50 +6922,50 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>56.03</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-0.58</v>
+        <v>0.96</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.73</v>
+        <v>41.79</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.85</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-89.30</t>
+          <t>-89.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3266</v>
+        <v>3641.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3154.6</t>
+          <t>3446.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5369.36</v>
+        <v>5420.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>195</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-439.4624580812879</t>
+          <t>-504.8901871323186</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1149.975956771535</t>
+          <t>-864.7426969129874</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7323,33 +7323,33 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7359,51 +7359,51 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>56.03</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.35</v>
+        <v>-0.58</v>
       </c>
       <c r="AI17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.43</v>
-      </c>
       <c r="AR17" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>0.93</v>
+        <v>-0.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,87 +8167,87 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>3.53</v>
+        <v>0.93</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.17</v>
+        <v>0.24</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ19" t="n">
         <v>0.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>3.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,67 +9454,67 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-1.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI22" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR22" t="n">
         <v>0.57</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,72 +9760,72 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-63.45</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-06-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>41.9</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-28.91</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-06-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-3.05</v>
+        <v>-1.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.94</v>
+        <v>0.57</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.4</v>
+        <v>41.42</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-85.34</t>
+          <t>-86.19</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,48 +9954,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78446.8684582744</t>
+          <t>78341.88983050847</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>7527</v>
+        <v>3751.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10587.5</t>
+          <t>10263.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5531.16</v>
+        <v>5439.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3060</t>
+          <t>-6511</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>881.4900656533426</t>
+          <t>621.8426610362237</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-408.0389746123274</t>
+          <t>-806.2180643579304</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2843.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>250.15</t>
+          <t>251.29</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10408.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>74.39</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>73.62</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>47.95</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6.06</v>
+        <v>0.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.97</v>
+        <v>5.49</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.17</v>
+        <v>48.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.77</v>
+        <v>48.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>208.23</t>
+          <t>441.53</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.60</t>
+          <t>-101.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>560590.0</t>
+          <t>265936.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>756681.2</v>
+        <v>781791.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>435826.9</t>
+          <t>448294.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>711662.52</v>
+        <v>712716.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>320854</t>
+          <t>333497</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-68797.0280623126</t>
+          <t>-55021.07238153565</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>57996.99817677308</t>
+          <t>20746.68386273761</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>560590.0</t>
+          <t>265936.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43439.0</t>
+          <t>10408.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,87 +1415,87 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>10.89</v>
+        <v>6.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.45</v>
+        <v>2.97</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.37</v>
+        <v>49.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.58</v>
+        <v>48.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>208.23</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.05</v>
+        <v>0.34</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-103.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>660301.2</v>
+        <v>756681.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>396119.5</t>
+          <t>435826.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>707273.86</v>
+        <v>711662.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>264181</t>
+          <t>320854</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-91850.48737850999</t>
+          <t>-68797.0280623126</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>77570.34011908178</t>
+          <t>57996.99817677308</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13274.0</t>
+          <t>43439.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,14 +1877,14 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>7.95</v>
+        <v>10.89</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.35</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1894,30 +1894,30 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.58</v>
+        <v>49.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.4</v>
+        <v>48.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.58</v>
+        <v>-0.47</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>211915.6</v>
+        <v>660301.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>175683.7</t>
+          <t>396119.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>699484.86</v>
+        <v>707273.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>264181</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-122654.2741962539</t>
+          <t>-91850.48737850999</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-87059.14782473008</t>
+          <t>77570.34011908178</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>13274.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.61</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.7</v>
+        <v>49.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.32</v>
+        <v>48.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-74.29</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1</v>
+        <v>-0.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>110484.2</v>
+        <v>211915.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>131708.6</t>
+          <t>175683.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>704283.76</v>
+        <v>699484.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-21224</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-129126.1153547128</t>
+          <t>-122654.2741962539</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-141058.6253221495</t>
+          <t>-87059.14782473008</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>78.61</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-7.05</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-114.05</t>
+          <t>-74.29</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>-1</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>-8.16</v>
+        <v>-7.05</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1964.0</t>
+          <t>1697.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.16</t>
+          <t>-38.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>71.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>59.47</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.82</v>
+        <v>0.06</v>
       </c>
       <c r="AI8" t="n">
-        <v>-8.68</v>
+        <v>-8.16</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.14</v>
+        <v>48.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-554.16</t>
+          <t>-214.93</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.78</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>131937.8</v>
+        <v>114972.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>220495.4</t>
+          <t>186641.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>753091.54</v>
+        <v>727463.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-88557</t>
+          <t>-71668</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-115339.9696769817</t>
+          <t>-122780.8078467799</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-170937.5362407448</t>
+          <t>-163705.4177806698</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>90325.0</t>
+          <t>78690.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3447.0</t>
+          <t>1964.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-46.04</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="AI9" t="n">
-        <v>-9.369999999999999</v>
+        <v>-8.68</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>46.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.95</v>
+        <v>50.68</v>
       </c>
       <c r="AN9" t="n">
-        <v>48.06</v>
+        <v>48.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1616.24</t>
+          <t>-554.16</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.9</v>
+        <v>-1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.31</t>
+          <t>-101.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>139451.8</v>
+        <v>131937.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>258423.6</t>
+          <t>220495.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>757640.24</v>
+        <v>753091.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-118971</t>
+          <t>-88557</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-105231.321210843</t>
+          <t>-115339.9696769817</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-176410.8291751111</t>
+          <t>-170937.5362407448</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>163051.0</t>
+          <t>90325.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2183.0</t>
+          <t>3447.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-44.25</t>
+          <t>-46.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="AI10" t="n">
-        <v>-10.99</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>51.31</v>
+        <v>50.95</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-381.16</t>
+          <t>-1616.24</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.84</v>
+        <v>-0.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-96.54</t>
+          <t>-99.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>152933</v>
+        <v>139451.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>274313.1</t>
+          <t>258423.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>755482.64</v>
+        <v>757640.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-121380</t>
+          <t>-118971</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-92289.59249006696</t>
+          <t>-105231.321210843</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-185721.5037536661</t>
+          <t>-176410.8291751111</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>101532.0</t>
+          <t>163051.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3047.0</t>
+          <t>2183.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-36.43</t>
+          <t>-44.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.39</v>
+        <v>2.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>-11.34</v>
+        <v>-10.99</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>51.58</v>
+        <v>51.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.69</v>
+        <v>47.88</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-229.04</t>
+          <t>-381.16</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.75</v>
+        <v>-0.84</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.58</v>
+        <v>0.3</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-96.54</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>225541.4</v>
+        <v>152933</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>354816.7</t>
+          <t>274313.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>754339.66</v>
+        <v>755482.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-129275</t>
+          <t>-121380</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-75301.97226032167</t>
+          <t>-92289.59249006696</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-185798.2351603996</t>
+          <t>-185721.5037536661</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>141265.0</t>
+          <t>101532.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3047.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-45.11</t>
+          <t>-36.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>13.76</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.67</v>
+        <v>-0.39</v>
       </c>
       <c r="AI12" t="n">
-        <v>-11.79</v>
+        <v>-11.34</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>46.04</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>52.19</v>
+        <v>51.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-154.91</t>
+          <t>-229.04</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.39</t>
+          <t>-93.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>688643.3834745763</t>
+          <t>688234.7242595204</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>258309.6</v>
+        <v>225541.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>470557.8</t>
+          <t>354816.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>752823.34</v>
+        <v>754339.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-212248</t>
+          <t>-129275</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-55211.74264212567</t>
+          <t>-75301.97226032167</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-183529.3073428617</t>
+          <t>-185798.2351603996</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>163516.0</t>
+          <t>141265.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>59.01</t>
+          <t>57.25</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5661,33 +5661,33 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.02</v>
+        <v>-0.9</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5696,26 +5696,26 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.5</v>
+        <v>43.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.94</v>
+        <v>41.99</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-18.59</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-90.10</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2748.0</t>
+          <t>3797.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3185</v>
+        <v>3522.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3291.3</t>
+          <t>3394.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>5467.14</v>
+        <v>5511.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-106</t>
+          <t>128</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-648.7459597111929</t>
+          <t>-656.9325580058278</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-823.6829975744886</t>
+          <t>-701.9588486263197</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2748.0</t>
+          <t>3797.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>43.1</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>43.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6083,61 +6083,61 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>65.47</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.71</v>
+        <v>0.02</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>43.49</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.42</v>
+        <v>43.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.89</v>
+        <v>41.94</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>-90.10</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3494.0</t>
+          <t>2748.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3015</v>
+        <v>3185</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3220.5</t>
+          <t>3291.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>5433.74</v>
+        <v>5467.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-205</t>
+          <t>-106</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-616.9392255542301</t>
+          <t>-648.7459597111929</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-855.7645318727846</t>
+          <t>-823.6829975744886</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>3494.0</t>
+          <t>2748.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6505,62 +6505,62 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>65.47</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.27</v>
+        <v>-0.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.36</v>
+        <v>43.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.84</v>
+        <v>41.89</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AQ15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR15" t="n">
         <v>0.45</v>
       </c>
-      <c r="AR15" t="n">
-        <v>0.46</v>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2879.8</v>
+        <v>3015</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3155.4</t>
+          <t>3220.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>5432</v>
+        <v>5433.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-205</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-573.5164425872202</t>
+          <t>-616.9392255542301</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-950.9608475891796</t>
+          <t>-855.7645318727846</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1737.0</t>
+          <t>3494.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6927,58 +6927,58 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.96</v>
+        <v>0.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>43.32</v>
+        <v>43.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.79</v>
+        <v>41.84</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AR16" t="n">
         <v>0.46</v>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3641.4</v>
+        <v>2879.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3446.2</t>
+          <t>3155.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>5420.44</v>
+        <v>5432</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-504.8901871323186</t>
+          <t>-573.5164425872202</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-864.7426969129874</t>
+          <t>-950.9608475891796</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>5837.0</t>
+          <t>1737.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7349,45 +7349,45 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>51.06</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>56.03</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.58</v>
+        <v>0.96</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.73</v>
+        <v>41.79</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7396,14 +7396,14 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.85</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.30</t>
+          <t>-89.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3266</v>
+        <v>3641.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3154.6</t>
+          <t>3446.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>5369.36</v>
+        <v>5420.44</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>195</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-439.4624580812879</t>
+          <t>-504.8901871323186</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1149.975956771535</t>
+          <t>-864.7426969129874</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2109.0</t>
+          <t>5837.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,22 +7523,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7781,51 +7781,51 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>56.03</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-0.35</v>
+        <v>-0.58</v>
       </c>
       <c r="AI18" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>43.35</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-15.85</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-12.59</t>
-        </is>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.43</v>
-      </c>
       <c r="AR18" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3397.6</v>
+        <v>3266</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3574.4</t>
+          <t>3154.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>5421.72</v>
+        <v>5369.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-176</t>
+          <t>111</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-310.2781855921521</t>
+          <t>-439.4624580812879</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1116.952900970476</t>
+          <t>-1149.975956771535</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1898.0</t>
+          <t>2109.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8193,61 +8193,61 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>51.06</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.93</v>
+        <v>-0.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>42.94</v>
+        <v>43.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-12.59</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3426</v>
+        <v>3397.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5476.5</t>
+          <t>3574.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>5434.38</v>
+        <v>5421.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2050</t>
+          <t>-176</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-163.610055523366</t>
+          <t>-310.2781855921521</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1007.278789077161</t>
+          <t>-1116.952900970476</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2818.0</t>
+          <t>1898.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -8615,61 +8615,61 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>3.53</v>
+        <v>0.93</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.17</v>
+        <v>0.24</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>42.81</v>
+        <v>42.94</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.59</v>
+        <v>41.65</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="AQ20" t="n">
         <v>0.46</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>-88.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3431</v>
+        <v>3426</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6140.5</t>
+          <t>5476.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>5446.08</v>
+        <v>5434.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2709</t>
+          <t>-2050</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-10.21574033176697</t>
+          <t>-163.610055523366</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-913.1986724768121</t>
+          <t>-1007.278789077161</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>5545.0</t>
+          <t>2818.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-53.63</t>
+          <t>-44.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9037,61 +9037,61 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>3.53</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-28.73</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3251</v>
+        <v>3431</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>7011.2</t>
+          <t>6140.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>5368.92</v>
+        <v>5446.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3760</t>
+          <t>-2709</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>153.9629746036958</t>
+          <t>-10.21574033176697</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1038.362839030714</t>
+          <t>-913.1986724768121</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>3960.0</t>
+          <t>5545.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,22 +9211,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-69.85</t>
+          <t>-53.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9459,61 +9459,61 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>0.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>42.6</v>
+        <v>42.66</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.46</v>
+        <v>41.51</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-28.81</t>
+          <t>-28.73</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-87.12</t>
+          <t>-87.98</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3043.2</v>
+        <v>3251</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10093.3</t>
+          <t>7011.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>5362.4</v>
+        <v>5368.92</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-7050</t>
+          <t>-3760</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>370.7494861735885</t>
+          <t>153.9629746036958</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1010.262975570905</t>
+          <t>-1038.362839030714</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2767.0</t>
+          <t>3960.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-63.45</t>
+          <t>-69.85</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9881,62 +9881,62 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-1.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI23" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-28.81</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR23" t="n">
         <v>0.57</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>42.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-24.76</t>
-        </is>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>4.39</t>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-87.12</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>78341.88983050847</t>
+          <t>78239.42665726376</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3751.2</v>
+        <v>3043.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10263.0</t>
+          <t>10093.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5439.54</v>
+        <v>5362.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-6511</t>
+          <t>-7050</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>621.8426610362237</t>
+          <t>370.7494861735885</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-806.2180643579304</t>
+          <t>-1010.262975570905</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2040.0</t>
+          <t>2767.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>251.29</t>
+          <t>251.49</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/微處理器.xlsx
+++ b/Result/checksun_type/微處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5060.0</t>
+          <t>4773.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>74.39</t>
+          <t>76.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,87 +993,87 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.95</v>
+        <v>-1.79</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.49</v>
+        <v>8.06</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>52.64000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>48.92</v>
+        <v>48.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.95</v>
+        <v>49.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>441.53</t>
+          <t>38123.21</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.71</t>
+          <t>-99.98</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>265936.0</t>
+          <t>249513.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>781791.6</v>
+        <v>815700</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>448294.0</t>
+          <t>463092.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>712716.3</v>
+        <v>713942.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>333497</t>
+          <t>352607</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-55021.07238153565</t>
+          <t>-47645.35790032335</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>20746.68386273761</t>
+          <t>-7078.928253655671</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>265936.0</t>
+          <t>249513.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10408.0</t>
+          <t>5060.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,74 +1320,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>74.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-3.07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>73.62</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>47.95</t>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>6.06</v>
+        <v>0.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.97</v>
+        <v>5.49</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.17</v>
+        <v>48.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.77</v>
+        <v>48.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>208.23</t>
+          <t>441.53</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.60</t>
+          <t>-101.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>560590.0</t>
+          <t>265936.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>756681.2</v>
+        <v>781791.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>435826.9</t>
+          <t>448294.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>711662.52</v>
+        <v>712716.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>320854</t>
+          <t>333497</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-68797.0280623126</t>
+          <t>-55021.07238153565</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>57996.99817677308</t>
+          <t>20746.68386273761</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>560590.0</t>
+          <t>265936.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43439.0</t>
+          <t>10408.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,87 +1837,87 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>10.89</v>
+        <v>6.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.45</v>
+        <v>2.97</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.37</v>
+        <v>49.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>48.58</v>
+        <v>48.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>208.23</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.05</v>
+        <v>0.34</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-103.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>660301.2</v>
+        <v>756681.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>396119.5</t>
+          <t>435826.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>707273.86</v>
+        <v>711662.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>264181</t>
+          <t>320854</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-91850.48737850999</t>
+          <t>-68797.0280623126</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>77570.34011908178</t>
+          <t>57996.99817677308</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2332253.0</t>
+          <t>560590.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13274.0</t>
+          <t>43439.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,14 +2299,14 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>7.95</v>
+        <v>10.89</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.35</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2316,30 +2316,30 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.58</v>
+        <v>49.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.4</v>
+        <v>48.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.58</v>
+        <v>-0.47</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>211915.6</v>
+        <v>660301.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>175683.7</t>
+          <t>396119.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>699484.86</v>
+        <v>707273.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>264181</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-122654.2741962539</t>
+          <t>-91850.48737850999</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-87059.14782473008</t>
+          <t>77570.34011908178</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>670208.0</t>
+          <t>2332253.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>18.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>13274.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.11</t>
+          <t>20.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.61</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>47.43</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.7</v>
+        <v>49.58</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.32</v>
+        <v>48.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-74.29</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1</v>
+        <v>-0.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.60</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>110484.2</v>
+        <v>211915.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>131708.6</t>
+          <t>175683.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>704283.76</v>
+        <v>699484.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-21224</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-129126.1153547128</t>
+          <t>-122654.2741962539</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-141058.6253221495</t>
+          <t>-87059.14782473008</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>79971.0</t>
+          <t>670208.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2959.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-16.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.89</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>78.61</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-7.05</v>
+        <v>-6.34</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.13</v>
+        <v>49.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.24</v>
+        <v>48.32</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-114.05</t>
+          <t>-74.29</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>-1</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-106.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>114796.4</v>
+        <v>110484.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>170168.9</t>
+          <t>131708.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>709757.14</v>
+        <v>704283.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-55372</t>
+          <t>-21224</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-126956.5680879061</t>
+          <t>-129126.1153547128</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-149923.2494141005</t>
+          <t>-141058.6253221495</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>140384.0</t>
+          <t>79971.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>57.25</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1697.0</t>
+          <t>2959.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.40</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>71.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.06</v>
+        <v>1.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>-8.16</v>
+        <v>-7.05</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.38</v>
+        <v>50.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>48.19</v>
+        <v>48.24</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-214.93</t>
+          <t>-114.05</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>688234.7242595204</t>
+          <t>687792.5197183099</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>114972.6</v>
+        <v>114796.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>186641.1</t>
+          <t>170168.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>727463.76</v>
+        <v>709757.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-71668</t>
+          <t>-55372</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-122780.8078467799</t>
+          <t>-126956.5680879061</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-163705.4177806698</t>
+          <t>-149923.2494141005</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>78690.0</t>
+          <t>140384.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>